--- a/utils/data-room-simulator/output/income_statement.xlsx
+++ b/utils/data-room-simulator/output/income_statement.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Income Statement" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,52 +417,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>cogs</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>gross_profit</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>opex</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>operating_income</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>gross_margin</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>operating_margin</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>net_margin</t>
         </is>
@@ -485,31 +473,31 @@
         <v>2021</v>
       </c>
       <c r="B2" t="n">
-        <v>43646228.04</v>
+        <v>24984607.29</v>
       </c>
       <c r="C2" t="n">
-        <v>9078415.439999999</v>
+        <v>6545967.100000001</v>
       </c>
       <c r="D2" t="n">
-        <v>34567812.6</v>
+        <v>18438640.18</v>
       </c>
       <c r="E2" t="n">
-        <v>26187736.82</v>
+        <v>14990764.39</v>
       </c>
       <c r="F2" t="n">
-        <v>8380075.780000001</v>
+        <v>3447875.789999999</v>
       </c>
       <c r="G2" t="n">
-        <v>8380075.790000001</v>
+        <v>3447875.81</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7919999998240398</v>
+        <v>0.7379999999991995</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1919999999156858</v>
+        <v>0.1379999993588052</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1920000001448006</v>
+        <v>0.1380000001592981</v>
       </c>
     </row>
     <row r="3">
@@ -517,31 +505,31 @@
         <v>2022</v>
       </c>
       <c r="B3" t="n">
-        <v>45705738.93</v>
+        <v>32340322.7</v>
       </c>
       <c r="C3" t="n">
-        <v>9506793.699999999</v>
+        <v>8473164.539999999</v>
       </c>
       <c r="D3" t="n">
-        <v>36198945.23</v>
+        <v>23867158.16</v>
       </c>
       <c r="E3" t="n">
-        <v>27423443.36</v>
+        <v>19404193.61</v>
       </c>
       <c r="F3" t="n">
-        <v>8775501.870000001</v>
+        <v>4462964.550000001</v>
       </c>
       <c r="G3" t="n">
-        <v>8775501.870000001</v>
+        <v>4462964.54</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7919999999439895</v>
+        <v>0.7380000002288164</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1919999999002314</v>
+        <v>0.1380000005380281</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1919999999002314</v>
+        <v>0.1380000002288165</v>
       </c>
     </row>
     <row r="4">
@@ -549,31 +537,31 @@
         <v>2023</v>
       </c>
       <c r="B4" t="n">
-        <v>48179930.91999999</v>
+        <v>38734236.98999999</v>
       </c>
       <c r="C4" t="n">
-        <v>10021425.63</v>
+        <v>10148370.1</v>
       </c>
       <c r="D4" t="n">
-        <v>38158505.28</v>
+        <v>28585866.9</v>
       </c>
       <c r="E4" t="n">
-        <v>28907958.55</v>
+        <v>23240542.2</v>
       </c>
       <c r="F4" t="n">
-        <v>9250546.729999997</v>
+        <v>5345324.699999996</v>
       </c>
       <c r="G4" t="n">
-        <v>9250546.75</v>
+        <v>5345324.689999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7919999998206725</v>
+        <v>0.7380000000356275</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1919999998621833</v>
+        <v>0.1379999998807256</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1920000002772939</v>
+        <v>0.1379999996225561</v>
       </c>
     </row>
     <row r="5">
@@ -581,31 +569,31 @@
         <v>2024</v>
       </c>
       <c r="B5" t="n">
-        <v>49914055.5</v>
+        <v>44396016.79</v>
       </c>
       <c r="C5" t="n">
-        <v>10382123.55</v>
+        <v>11631756.4</v>
       </c>
       <c r="D5" t="n">
-        <v>39531931.98</v>
+        <v>32764260.38</v>
       </c>
       <c r="E5" t="n">
-        <v>29948433.3</v>
+        <v>26637610.07</v>
       </c>
       <c r="F5" t="n">
-        <v>9583498.680000007</v>
+        <v>6126650.309999995</v>
       </c>
       <c r="G5" t="n">
-        <v>9583498.67</v>
+        <v>6126650.310000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7920000004808265</v>
+        <v>0.7379999997517794</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1920000004808266</v>
+        <v>0.1379999998418776</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1920000002804821</v>
+        <v>0.1379999998418777</v>
       </c>
     </row>
     <row r="6">
@@ -613,31 +601,31 @@
         <v>2025</v>
       </c>
       <c r="B6" t="n">
-        <v>60616961.61</v>
+        <v>54030253.73</v>
       </c>
       <c r="C6" t="n">
-        <v>12608328</v>
+        <v>14155926.48</v>
       </c>
       <c r="D6" t="n">
-        <v>48008633.61000001</v>
+        <v>39874327.23999999</v>
       </c>
       <c r="E6" t="n">
-        <v>36370176.97000001</v>
+        <v>32418152.24</v>
       </c>
       <c r="F6" t="n">
-        <v>11638456.64</v>
+        <v>7456174.999999993</v>
       </c>
       <c r="G6" t="n">
-        <v>11638456.64</v>
+        <v>7456175.01</v>
       </c>
       <c r="H6" t="n">
-        <v>0.792000000245476</v>
+        <v>0.7379999997642062</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1920000001794877</v>
+        <v>0.1379999997271897</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1920000001794877</v>
+        <v>0.1379999999122714</v>
       </c>
     </row>
     <row r="7">
@@ -645,31 +633,31 @@
         <v>2026</v>
       </c>
       <c r="B7" t="n">
-        <v>4693332.11</v>
+        <v>8525699.129999999</v>
       </c>
       <c r="C7" t="n">
-        <v>976213.08</v>
+        <v>2233733.17</v>
       </c>
       <c r="D7" t="n">
-        <v>3717119.03</v>
+        <v>6291965.96</v>
       </c>
       <c r="E7" t="n">
-        <v>2815999.27</v>
+        <v>5115419.48</v>
       </c>
       <c r="F7" t="n">
-        <v>901119.7599999998</v>
+        <v>1176546.48</v>
       </c>
       <c r="G7" t="n">
-        <v>901119.76</v>
+        <v>1176546.48</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7919999997613635</v>
+        <v>0.7380000002416225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1919999989090906</v>
+        <v>0.1380000000070375</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1919999989090906</v>
+        <v>0.1380000000070375</v>
       </c>
     </row>
   </sheetData>
